--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -105,12 +105,27 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>DNK05463</t>
+  </si>
+  <si>
+    <t>DNK05465</t>
+  </si>
+  <si>
+    <t>DNK05467</t>
+  </si>
+  <si>
+    <t>DNK05469</t>
+  </si>
+  <si>
     <t>DNK05472</t>
   </si>
   <si>
     <t>DNK05473</t>
   </si>
   <si>
+    <t>NPU02193</t>
+  </si>
+  <si>
     <t>NPU03011</t>
   </si>
   <si>
@@ -166,6 +181,9 @@
   </si>
   <si>
     <t>MCS88194</t>
+  </si>
+  <si>
+    <t>MCS88214</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.184.100.8</t>
@@ -459,7 +477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -526,16 +544,46 @@
       <c r="A10" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>37</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
         <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +593,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -562,78 +610,84 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>37</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -660,24 +714,24 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -704,54 +758,54 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-observation-codes.xlsx
+++ b/fhir/ValueSet-ehealth-observation-codes.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -192,6 +193,9 @@
     <t>ZZ3170</t>
   </si>
   <si>
+    <t>ZZ5048</t>
+  </si>
+  <si>
     <t>urn:oid:1.2.208.176.2.4</t>
   </si>
   <si>
@@ -214,6 +218,27 @@
   </si>
   <si>
     <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-I</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IA</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IB</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-II</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-III</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IV</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/cs/mds-codes</t>
   </si>
 </sst>
 </file>
@@ -697,7 +722,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -720,18 +745,24 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>42</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>58</v>
+      <c r="B5" t="s" s="2">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -758,37 +789,37 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2"/>
     </row>
@@ -805,7 +836,81 @@
         <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
